--- a/docs/ai-workshop/月度盘点工作流拆解-补充版.xlsx
+++ b/docs/ai-workshop/月度盘点工作流拆解-补充版.xlsx
@@ -7,13 +7,12 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="月度盘点-原有工作流" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="对照说明与补充要点" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="精简版-可粘贴回模板" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="AI场景工作流梳理表" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="AI步骤与左侧对照" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="原有工作流-确认版" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="确认与下一步" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'月度盘点-原有工作流'!$A$3:$I$11</definedName>
-  </definedNames>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -21,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -37,18 +36,30 @@
     </font>
     <font>
       <name val="微软雅黑"/>
-      <color rgb="00666666"/>
-      <sz val="9"/>
+      <b val="1"/>
+      <color rgb="001F4E79"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <b val="1"/>
+      <color rgb="00C65911"/>
+      <sz val="11"/>
     </font>
     <font>
       <name val="微软雅黑"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="11"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="微软雅黑"/>
-      <sz val="10"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <color rgb="00666666"/>
+      <sz val="9"/>
     </font>
     <font>
       <name val="微软雅黑"/>
@@ -56,7 +67,7 @@
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -65,22 +76,32 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F4E79"/>
+        <fgColor rgb="00D6EAF8"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F2F2F2"/>
+        <fgColor rgb="002E75B6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCE4EC"/>
+        <fgColor rgb="00C65911"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F7F7F7"/>
       </patternFill>
     </fill>
   </fills>
@@ -110,40 +131,51 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -512,472 +544,598 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
-    <col width="28" customWidth="1" min="5" max="5"/>
-    <col width="32" customWidth="1" min="6" max="6"/>
-    <col width="32" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="28" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="7" max="7"/>
+    <col width="32" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="28" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
+    <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>线上学习资源盘点 · 二级流程「月度盘点」· 原有工作流拆解（补充版）</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="48" customHeight="1">
+          <t>业务场景工作流梳理表｜一级：线上学习资源盘点｜二级：月度盘点</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>对齐依据：业务梳理表三级流程——①汇总上月使用分析与异常；②收集业务变化与用户/业务反馈；③重点资源评估并识别缺口与紧急需求；④形成月度盘点结论并滚动更新缺口与迭代建议。输入：月度运营数据、用户反馈、业务需求变更、上期盘点结论；输出：月度盘点结论、资源标签更新、资源需求清单。</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
+          <t>原有工作流（已确认）</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>AI优化后工作流（人机协同，步数可不与左侧一一对应）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>步骤</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>环节名称</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>现在由谁做</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>当前做法</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>输入材料</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>输出结果</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>当前问题</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>对应三级流程要点</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>本次处理说明</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="95" customHeight="1">
-      <c r="A4" s="4" t="n">
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>人做什么</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>AI做什么</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>AI实现类型</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>输出结果</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>是否人工确认</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="110" customHeight="1">
+      <c r="A4" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>多源取数与基础表导入</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>罗阳先</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>1. 从海味平台后台、知识库、组织/花名册等源系统分别导出原始 Excel；
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>【多源取数与基础表导入】
+1. 从海味平台后台、知识库、组织/花名册等源系统分别导出原始 Excel；
 2. 将可用课程清单、在线课程导出、在线课程学习表、个人学习情况（周/年）、知识管理、员工花名册等导入自制分析工具（SQLite）；
 3. 校验表名与列名是否匹配白名单，不合格则退回重导。</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>平台后台、知识库、花名册等原始数据；上月运营相关导出权限</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>SQLite 中 7 张基础表（可用课程清单、在线课程导出、在线课程学习表、个人学习情况周、个人学习情况年、知识管理、员工花名册）</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>①数据分散在多系统，需反复手工导出，耗时长、易漏导；
 ②列名/格式须严格匹配，非白名单表不可导入，失败后需重跑；
 ③缺少统一取数口径与批次号，难回溯当月取数版本。</t>
         </is>
       </c>
-      <c r="H4" s="5" t="inlineStr">
-        <is>
-          <t>为“汇总上月使用分析数据”提供数据底座</t>
-        </is>
-      </c>
-      <c r="I4" s="6" t="inlineStr">
-        <is>
-          <t>合并原步骤1“源系统取数”与步骤2“基础表导出”，消除重复；补齐校验与版本回溯问题</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="95" customHeight="1">
-      <c r="A5" s="7" t="n">
+      <c r="G4" s="7" t="inlineStr">
+        <is>
+          <t>1. 设定本月盘点范围与取数批次，发起取数；
+2. 处理校验失败项并补导缺失表；
+3. 确认本月口径（人数/完成率等）无争议。</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
+          <t>1. 按白名单校验表名/列名/必填字段；
+2. 生成取数完整性与口径差异报告；
+3. 标记缺失表、异常字段与建议重导清单。</t>
+        </is>
+      </c>
+      <c r="I4" s="7" t="inlineStr">
+        <is>
+          <t>规则校验 + 数据质量助手</t>
+        </is>
+      </c>
+      <c r="J4" s="7" t="inlineStr">
+        <is>
+          <t>已校验基础数据集（含批次号）；取数质量报告；待补导清单</t>
+        </is>
+      </c>
+      <c r="K4" s="8" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="110" customHeight="1">
+      <c r="A5" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="B5" s="8" t="inlineStr">
-        <is>
-          <t>分析表生成（清单+使用统计）</t>
-        </is>
-      </c>
-      <c r="C5" s="8" t="inlineStr">
+      <c r="B5" s="10" t="inlineStr">
         <is>
           <t>罗阳先</t>
         </is>
       </c>
-      <c r="D5" s="8" t="inlineStr">
-        <is>
-          <t>使用自制软件按固定顺序对基础表进行分析汇总，生成课程清单类与统计类结果表；同时汇总上月浏览/学习人数/完成率/时长等使用指标，为后续异常识别做准备。</t>
-        </is>
-      </c>
-      <c r="E5" s="8" t="inlineStr">
+      <c r="C5" s="10" t="inlineStr">
+        <is>
+          <t>【分析表生成（清单+使用统计）】
+使用自制软件按固定顺序对基础表进行分析汇总，生成课程清单类与统计类结果表；同时汇总上月浏览/学习人数/完成率/时长等使用指标，为后续异常识别做准备。</t>
+        </is>
+      </c>
+      <c r="D5" s="10" t="inlineStr">
         <is>
           <t>上述 7 张基础表</t>
         </is>
       </c>
-      <c r="F5" s="8" t="inlineStr">
+      <c r="E5" s="10" t="inlineStr">
         <is>
           <t>海味课程月度清单、海味课程目录、课程数据统计、上周/上月新课清单、上周/上月新知识清单；上月资源使用统计底表</t>
         </is>
       </c>
-      <c r="G5" s="8" t="inlineStr">
+      <c r="F5" s="10" t="inlineStr">
         <is>
           <t>①须先导齐全部基础表，依赖顺序强，失败需整段重跑；
 ②大表运算偏慢；
 ③使用指标口径（人数、完成率等）部分仍需人工核对。</t>
         </is>
       </c>
-      <c r="H5" s="8" t="inlineStr">
-        <is>
-          <t>汇总上月线上学习资源使用分析数据</t>
-        </is>
-      </c>
-      <c r="I5" s="6" t="inlineStr">
-        <is>
-          <t>保留原“分析表生成”；补充使用统计输出，对齐三级流程第1点</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="95" customHeight="1">
-      <c r="A6" s="4" t="n">
+      <c r="G5" s="10" t="inlineStr">
+        <is>
+          <t>1. 确认分析表生成成功；
+2. 抽检关键指标口径；
+3. 确定本月重点关注资源范围。</t>
+        </is>
+      </c>
+      <c r="H5" s="10" t="inlineStr">
+        <is>
+          <t>1. 自动汇总生成课程月度清单、目录、统计、新课/新知识表；
+2. 汇总上月使用指标（学习人数、完成率、时长等）；
+3. 输出使用洞察草稿（环比异动、头部/尾部资源）。</t>
+        </is>
+      </c>
+      <c r="I5" s="10" t="inlineStr">
+        <is>
+          <t>数据分析助手（汇总统计 + 洞察草稿）</t>
+        </is>
+      </c>
+      <c r="J5" s="10" t="inlineStr">
+        <is>
+          <t>分析表全套；上月使用统计底表；使用洞察草稿</t>
+        </is>
+      </c>
+      <c r="K5" s="8" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="110" customHeight="1">
+      <c r="A6" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>异常与信息不规范识别</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>罗阳先</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>1. 在海味课程月度清单中核查目录、部门归属、标题、课程简介、讲师、封面、标签、大纲、面向对象等字段是否规范完整；
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>【异常与信息不规范识别】
+1. 在海味课程月度清单中核查目录、部门归属、标题、课程简介、讲师、封面、标签、大纲、面向对象等字段是否规范完整；
 2. 结合使用统计，识别异常资源（如完成率骤降、零学习、差评集中、长期无更新等）；
 3. 形成待整改清单与异常初判清单。</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>海味课程月度清单、课程数据统计/使用统计底表、盘点核对标准（如有）</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>信息不规范课程清单；使用异常资源初判清单；拟整改项说明</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>①异常识别高度依赖个人经验，规则未固化，易遗漏；
 ②信息不规范与使用异常两套判断混在一起，缺少标准检查清单；
 ③异常结论缺少留痕，难与上期对比。</t>
         </is>
       </c>
-      <c r="H6" s="5" t="inlineStr">
-        <is>
-          <t>汇总使用分析数据与关键异常</t>
-        </is>
-      </c>
-      <c r="I6" s="6" t="inlineStr">
-        <is>
-          <t>由原“数据查看与处理”拆出并强化；补“使用异常”维度与输出物</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="95" customHeight="1">
-      <c r="A7" s="7" t="n">
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>1. 审定异常规则阈值；
+2. 确认不规范字段判定标准；
+3. 裁定争议项（误报剔除/漏报复核）。</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
+          <t>1. 按规则+语义检查识别字段不规范（目录/归属/标题/简介/讲师/封面/标签/大纲/对象等）；
+2. 识别使用异常（零学习、完成率骤降、差评集中、长期未更新等）；
+3. 输出待整改清单与异常初判清单（含理由）。</t>
+        </is>
+      </c>
+      <c r="I6" s="7" t="inlineStr">
+        <is>
+          <t>规则引擎 + LLM初筛</t>
+        </is>
+      </c>
+      <c r="J6" s="7" t="inlineStr">
+        <is>
+          <t>信息不规范清单；使用异常初判清单；规则命中说明</t>
+        </is>
+      </c>
+      <c r="K6" s="8" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="110" customHeight="1">
+      <c r="A7" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="B7" s="8" t="inlineStr">
-        <is>
-          <t>业务变化与用户/业务反馈收集</t>
-        </is>
-      </c>
-      <c r="C7" s="8" t="inlineStr">
+      <c r="B7" s="10" t="inlineStr">
         <is>
           <t>罗阳先（牵头）；业务方/分院管理员（提供反馈）</t>
         </is>
       </c>
-      <c r="D7" s="8" t="inlineStr">
-        <is>
-          <t>1. 收集本月业务发展变化、战略/项目重点调整信息；
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>【业务变化与用户/业务反馈收集】
+1. 收集本月业务发展变化、战略/项目重点调整信息；
 2. 汇总用户与业务方对资源的反馈（缺失主题、内容过时、急需补课等）；
 3. 调阅上期盘点结论与未闭环事项，形成本月输入包。</t>
         </is>
       </c>
-      <c r="E7" s="8" t="inlineStr">
+      <c r="D7" s="10" t="inlineStr">
         <is>
           <t>业务需求变更信息、用户/业务方反馈、上期盘点结论与待办、相关会议纪要或飞书文档</t>
         </is>
       </c>
-      <c r="F7" s="8" t="inlineStr">
+      <c r="E7" s="10" t="inlineStr">
         <is>
           <t>本月业务变化与反馈汇总表；上期未闭环事项清单</t>
         </is>
       </c>
-      <c r="G7" s="8" t="inlineStr">
+      <c r="F7" s="10" t="inlineStr">
         <is>
           <t>①反馈渠道分散（群聊、口头、文档），收集不完整、难结构化；
 ②缺少固定收集节奏与责任人，容易遗漏紧急需求；
 ③与数据侧异常清单未打通，后续评估靠人工拼接。</t>
         </is>
       </c>
-      <c r="H7" s="8" t="inlineStr">
-        <is>
-          <t>收集业务发展变化信息及用户/业务方反馈</t>
-        </is>
-      </c>
-      <c r="I7" s="6" t="inlineStr">
-        <is>
-          <t>原表缺失，按三级流程第2点新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="95" customHeight="1">
-      <c r="A8" s="4" t="n">
+      <c r="G7" s="10" t="inlineStr">
+        <is>
+          <t>1. 发起本月反馈收集（分院/业务方）；
+2. 补充关键业务变化口头信息；
+3. 确认紧急需求优先级。</t>
+        </is>
+      </c>
+      <c r="H7" s="10" t="inlineStr">
+        <is>
+          <t>1. 归并分散反馈（文档/表格/纪要）并结构化；
+2. 对照上期未闭环事项生成跟踪表；
+3. 将反馈主题与资源缺口候选自动关联。</t>
+        </is>
+      </c>
+      <c r="I7" s="10" t="inlineStr">
+        <is>
+          <t>文档理解 + 结构化归并助手</t>
+        </is>
+      </c>
+      <c r="J7" s="10" t="inlineStr">
+        <is>
+          <t>业务变化与反馈汇总表；上期未闭环跟踪表；反馈-缺口关联初稿</t>
+        </is>
+      </c>
+      <c r="K7" s="8" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="110" customHeight="1">
+      <c r="A8" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>课程信息整改闭环</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="B8" s="7" t="inlineStr">
         <is>
           <t>罗阳先（发起与跟踪）；课程发布人（修改落地）</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>依据信息不规范清单，联系对应课程发布人，在海味平台完成目录、归属、标题、简介、讲师、封面、标签、大纲、面向对象等字段整改；罗阳先复核是否达标。</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>【课程信息整改闭环】
+依据信息不规范清单，联系对应课程发布人，在海味平台完成目录、归属、标题、简介、讲师、封面、标签、大纲、面向对象等字段整改；罗阳先复核是否达标。</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
         <is>
           <t>信息不规范课程清单；课程发布人联系方式；平台编辑权限</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>已整改课程清单；未整改/超期清单；平台侧字段更新结果</t>
         </is>
       </c>
-      <c r="G8" s="5" t="inlineStr">
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t>①靠人工逐个联系催改，协同成本高、进度不可视；
 ②发布人响应不及时导致盘点结论滞后；
 ③整改标准执行不一致，返工多。</t>
         </is>
       </c>
-      <c r="H8" s="5" t="inlineStr">
-        <is>
-          <t>支撑资源质量与标签可维护（为盘点结论与标签更新铺垫）</t>
-        </is>
-      </c>
-      <c r="I8" s="6" t="inlineStr">
-        <is>
-          <t>保留原“课程信息修改”；补齐输出物与问题描述（原“人数靠手工”与本环节不匹配，已纠正）</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="95" customHeight="1">
-      <c r="A9" s="7" t="n">
+      <c r="G8" s="7" t="inlineStr">
+        <is>
+          <t>1. 确认整改清单与责任发布人；
+2. 下发催改并跟踪超期；
+3. 复核整改是否达标。
+（课程发布人：在平台完成修改）</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
+          <t>1. 按课程自动匹配发布人并生成催办草稿/整改说明；
+2. 汇总已改/未改/超期状态；
+3. 对已改项做字段合规复检。</t>
+        </is>
+      </c>
+      <c r="I8" s="7" t="inlineStr">
+        <is>
+          <t>工单/催办助手 + 合规复检</t>
+        </is>
+      </c>
+      <c r="J8" s="7" t="inlineStr">
+        <is>
+          <t>整改工单包；进度看板（已改/未改/超期）；复检结果</t>
+        </is>
+      </c>
+      <c r="K8" s="8" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="110" customHeight="1">
+      <c r="A9" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="B9" s="8" t="inlineStr">
-        <is>
-          <t>重点资源评估与缺口/紧急需求识别</t>
-        </is>
-      </c>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="B9" s="10" t="inlineStr">
         <is>
           <t>罗阳先（初评）；业务专家/管理员（确认）</t>
         </is>
       </c>
-      <c r="D9" s="8" t="inlineStr">
-        <is>
-          <t>1. 结合使用数据、异常清单、业务反馈，对重点资源做月度评估；
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>【重点资源评估与缺口/紧急需求识别】
+1. 结合使用数据、异常清单、业务反馈，对重点资源做月度评估；
 2. 识别新增缺口与紧急需求（主题、对象、形式、优先级）；
 3. 滚动更新资源健康度/运营标签建议（高价值/待优化/建议下架等，月度以滚动更新为主）。</t>
         </is>
       </c>
-      <c r="E9" s="8" t="inlineStr">
+      <c r="D9" s="10" t="inlineStr">
         <is>
           <t>使用统计与异常清单、业务变化与反馈汇总、上期缺口清单、资源目录</t>
         </is>
       </c>
-      <c r="F9" s="8" t="inlineStr">
+      <c r="E9" s="10" t="inlineStr">
         <is>
           <t>重点资源评估表；新增缺口与紧急需求清单；资源标签更新建议</t>
         </is>
       </c>
-      <c r="G9" s="8" t="inlineStr">
+      <c r="F9" s="10" t="inlineStr">
         <is>
           <t>①评估标准不统一，经验依赖强；
 ②缺口与紧急需求缺少量化优先级；
 ③标签更新建议到平台落标缺少固定动作。</t>
         </is>
       </c>
-      <c r="H9" s="8" t="inlineStr">
-        <is>
-          <t>对重点资源定期评估，识别新增缺口与紧急需求；滚动更新标签</t>
-        </is>
-      </c>
-      <c r="I9" s="6" t="inlineStr">
-        <is>
-          <t>原表缺失，按三级流程第3点及输出“资源标签更新/资源需求清单”新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="95" customHeight="1">
-      <c r="A10" s="4" t="n">
+      <c r="G9" s="10" t="inlineStr">
+        <is>
+          <t>1. 确认重点资源评估结论；
+2. 裁定标签更新与缺口/紧急需求优先级；
+3. 明确需移交规划的事项。</t>
+        </is>
+      </c>
+      <c r="H9" s="10" t="inlineStr">
+        <is>
+          <t>1. 综合使用数据、异常、反馈生成重点资源评估草稿；
+2. 给出健康度/运营标签建议与缺口、紧急需求清单草稿；
+3. 提出迭代建议与规划承接建议。</t>
+        </is>
+      </c>
+      <c r="I9" s="10" t="inlineStr">
+        <is>
+          <t>评估建议助手（多源综合推理）</t>
+        </is>
+      </c>
+      <c r="J9" s="10" t="inlineStr">
+        <is>
+          <t>重点资源评估表；标签更新建议；缺口与紧急需求清单；迭代建议草稿</t>
+        </is>
+      </c>
+      <c r="K9" s="8" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="110" customHeight="1">
+      <c r="A10" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>形成月度盘点结论</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="B10" s="7" t="inlineStr">
         <is>
           <t>罗阳先（起草）；业务专家（确认）</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>汇总本月清单治理结果、使用与异常洞察、反馈与缺口识别，形成《月度盘点结论》（含：现状摘要、异常与整改情况、缺口与紧急需求、迭代建议、需规划承接事项）。</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>【形成月度盘点结论】
+汇总本月清单治理结果、使用与异常洞察、反馈与缺口识别，形成《月度盘点结论》（含：现状摘要、异常与整改情况、缺口与紧急需求、迭代建议、需规划承接事项）。</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
         <is>
           <t>已整改结果、异常与评估表、缺口与紧急需求清单、上期盘点结论</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>《月度盘点结论》；滚动更新后的资源需求/迭代建议清单</t>
         </is>
       </c>
-      <c r="G10" s="5" t="inlineStr">
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>①从多份表到成文靠人工拼接，耗时长；
 ②结论口径月度间不一致，难对比；
 ③与规划环节的交接物不固定，易断档。</t>
         </is>
       </c>
-      <c r="H10" s="5" t="inlineStr">
-        <is>
-          <t>形成月度盘点结论，滚动更新缺口与迭代建议</t>
-        </is>
-      </c>
-      <c r="I10" s="6" t="inlineStr">
-        <is>
-          <t>原表缺失，按三级流程第4点及输出“月度盘点结论、资源需求清单”新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="95" customHeight="1">
-      <c r="A11" s="7" t="n">
+      <c r="G10" s="7" t="inlineStr">
+        <is>
+          <t>1. 审定《月度盘点结论》并发布；
+2. 确认管理员清单终版；
+3. 将规划承接事项正式移交。</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
+          <t>1. 一键生成《月度盘点结论》初稿（现状/异常与整改/缺口/迭代建议）；
+2. 生成面向管理员的清单说明与飞书同步文案；
+3. 检查本月交付物是否齐全（结论、标签建议、需求清单、课程清单）。</t>
+        </is>
+      </c>
+      <c r="I10" s="7" t="inlineStr">
+        <is>
+          <t>报告生成助手 + 分发文案助手</t>
+        </is>
+      </c>
+      <c r="J10" s="7" t="inlineStr">
+        <is>
+          <t>《月度盘点结论》初稿/定稿稿；管理员课程清单终版；同步文案；交付物齐全性检查结果；规划移交清单</t>
+        </is>
+      </c>
+      <c r="K10" s="8" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="110" customHeight="1">
+      <c r="A11" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="B11" s="8" t="inlineStr">
-        <is>
-          <t>结果发布与管理员同步</t>
-        </is>
-      </c>
-      <c r="C11" s="8" t="inlineStr">
+      <c r="B11" s="10" t="inlineStr">
         <is>
           <t>罗阳先</t>
         </is>
       </c>
-      <c r="D11" s="8" t="inlineStr">
-        <is>
-          <t>1. 发布《海味课程月度清单》供各级管理员查阅使用（因其日常权限无法看全平台课程）；
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>【结果发布与管理员同步】
+1. 发布《海味课程月度清单》供各级管理员查阅使用（因其日常权限无法看全平台课程）；
 2. 同步月度盘点结论、缺口/需求清单至飞书等渠道；
 3. 将需规划承接事项移交“线上学习资源规划”。</t>
         </is>
       </c>
-      <c r="E11" s="8" t="inlineStr">
+      <c r="D11" s="10" t="inlineStr">
         <is>
           <t>海味课程月度清单终版、《月度盘点结论》、资源需求/迭代建议清单</t>
         </is>
       </c>
-      <c r="F11" s="8" t="inlineStr">
+      <c r="E11" s="10" t="inlineStr">
         <is>
           <t>管理员可用的全量/月度课程清单；已同步的盘点结论与需求清单；向规划环节的移交记录</t>
         </is>
       </c>
-      <c r="G11" s="8" t="inlineStr">
+      <c r="F11" s="10" t="inlineStr">
         <is>
           <t>①与飞书等汇报渠道仍需人工粘贴，无自动对接；
 ②清单、结论、需求多份材料分发，版本易乱；
 ③管理员是否取用、是否反馈缺少闭环。</t>
         </is>
       </c>
-      <c r="H11" s="8" t="inlineStr">
-        <is>
-          <t>交付月度盘点输出，衔接规划</t>
-        </is>
-      </c>
-      <c r="I11" s="6" t="inlineStr">
-        <is>
-          <t>由原“结果导出与使用”升级：保留清单发布价值，补盘点结论与需求清单同步</t>
+      <c r="G11" s="11" t="inlineStr"/>
+      <c r="H11" s="11" t="inlineStr"/>
+      <c r="I11" s="11" t="inlineStr"/>
+      <c r="J11" s="11" t="inlineStr"/>
+      <c r="K11" s="11" t="inlineStr"/>
+    </row>
+    <row r="13" ht="85" customHeight="1">
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>注意事项：
+1、左侧原有工作流已确认（8步）；右侧AI优化后工作流重构为7步，不一一对应。
+2、右侧输出覆盖左侧：质量合格基础数据、分析表与使用统计、不规范/异常清单、反馈汇总、整改闭环、评估与标签/缺口、月度盘点结论、管理员清单及同步移交。
+3、左侧问题对应解决：多源手工导出与格式失败→AI步骤1；汇总慢易错→2；异常靠经验→3；反馈分散→4；催改难跟踪→5；评估缺标准→6；结论与分发耗时/版本乱→7。
+4、AI适配总原则：AI可辅助数据汇总清洗、异常提示、缺口与迭代建议草稿；人工确认月度盘点结论发布及相关决策。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:I11"/>
-  <mergeCells count="2">
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A2:I2"/>
+  <mergeCells count="4">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="G2:K2"/>
+    <mergeCell ref="A13:K13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -989,323 +1147,361 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="9" t="inlineStr">
-        <is>
-          <t>月度盘点工作流：原表问题诊断与本次补充说明</t>
+      <c r="A1" s="13" t="inlineStr">
+        <is>
+          <t>AI优化后步骤说明（确认版左侧 → 右侧人机协同）</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="10" t="inlineStr">
-        <is>
-          <t>一、原表与三级流程对照</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>三级流程要求</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>原工作流覆盖情况</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>缺口判断</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>补充后对应步骤</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>1. 汇总上月使用分析数据与关键异常</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>有取数/分析表，偏清单与统计；异常识别弱</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>部分覆盖</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>步骤1-3</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>2. 收集业务发展变化及用户/业务方反馈</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>无对应环节</t>
-        </is>
-      </c>
-      <c r="C6" s="11" t="inlineStr">
-        <is>
-          <t>缺失</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>步骤4（新增）</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>3. 重点资源评估，识别新增缺口与紧急需求</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>无对应环节；仅有课程信息不规范修改</t>
-        </is>
-      </c>
-      <c r="C7" s="11" t="inlineStr">
-        <is>
-          <t>缺失</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>步骤6（新增）</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>4. 形成月度盘点结论，滚动更新缺口与迭代建议</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>仅有“发布月度课程清单”</t>
-        </is>
-      </c>
-      <c r="C8" s="11" t="inlineStr">
-        <is>
-          <t>缺失/偏离</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>步骤7-8</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>输出：月度盘点结论</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="C9" s="11" t="inlineStr">
-        <is>
-          <t>缺失</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>步骤7</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>输出：资源标签更新</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>无明确环节</t>
-        </is>
-      </c>
-      <c r="C10" s="11" t="inlineStr">
-        <is>
-          <t>缺失</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>步骤6</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>输出：资源需求清单</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="C11" s="11" t="inlineStr">
-        <is>
-          <t>缺失</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>步骤6-7</t>
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>AI优化后步骤</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>主要解决的原问题</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>主要覆盖的原步骤</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>人工确认要点</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>1. 取数批次发起与质量校验</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>多系统手工导出、格式不匹配、难回溯</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>原1</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>口径确认、补导决策</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="36" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>2. 分析表与使用洞察自动生成</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>须导齐才跑、重跑慢、口径靠人工核对</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>原2</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>抽检口径、圈定重点范围</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="36" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>3. 不规范与使用异常智能初筛</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>异常靠经验、易遗漏、缺少留痕</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>原3</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>裁定误报/漏报、确认规则</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="36" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>4. 反馈结构化归并与缺口关联</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>反馈分散、缺节奏、难与数据拼接</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>原4</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>确认紧急需求与业务变化</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="36" customHeight="1">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>5. 整改工单催办与合规复检</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>人工催改、进度不可视、标准不一</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>原5</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>下发催改、复核达标</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="36" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>6. 评估/标签/缺口建议生成</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>评估经验依赖、优先级不量化</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>原6</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>裁定标签与优先级、移交规划事项</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="36" customHeight="1">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>7. 结论成文、清单发布与同步</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>成文拼接耗时、飞书粘贴、版本乱</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>原7+原8</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>审定发布结论、确认移交</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="14" t="inlineStr">
+        <is>
+          <t>交付物覆盖检查（右侧应包住左侧）</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="10" t="inlineStr">
-        <is>
-          <t>二、原表结构问题与处理</t>
+      <c r="A13" s="15" t="inlineStr">
+        <is>
+          <t>左侧关键输出</t>
+        </is>
+      </c>
+      <c r="B13" s="15" t="inlineStr">
+        <is>
+          <t>右侧何处覆盖</t>
+        </is>
+      </c>
+      <c r="C13" s="15" t="inlineStr">
+        <is>
+          <t>状态</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="12" t="inlineStr">
-        <is>
-          <t>问题</t>
-        </is>
-      </c>
-      <c r="B14" s="12" t="inlineStr">
-        <is>
-          <t>处理方式</t>
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>7张基础表/可用数据集</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>AI步骤1</t>
+        </is>
+      </c>
+      <c r="C14" s="16" t="inlineStr">
+        <is>
+          <t>已覆盖</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>步骤1“源系统取数”与步骤2“基础表导出”高度重复</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>合并为步骤1“多源取数与基础表导入”</t>
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>分析表+使用统计</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>AI步骤2</t>
+        </is>
+      </c>
+      <c r="C15" s="16" t="inlineStr">
+        <is>
+          <t>已覆盖</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>步骤4输出写成“在海味平台上进行修改”，是动作不是交付物</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>改为不规范清单/异常清单等可交接输出</t>
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>不规范清单+异常初判</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>AI步骤3</t>
+        </is>
+      </c>
+      <c r="C16" s="16" t="inlineStr">
+        <is>
+          <t>已覆盖</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>步骤5问题“人数仍靠手工”与“联系发布人改课”不匹配</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>重写为催改协同、标准不一致、进度不可视</t>
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>业务变化与反馈汇总</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>AI步骤4</t>
+        </is>
+      </c>
+      <c r="C17" s="16" t="inlineStr">
+        <is>
+          <t>已覆盖</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>步骤6仅发布清单，未覆盖盘点结论与需求清单</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>拆为步骤7结论 + 步骤8发布同步，并保留清单对管理员的价值说明</t>
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>已整改/未整改清单</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>AI步骤5</t>
+        </is>
+      </c>
+      <c r="C18" s="16" t="inlineStr">
+        <is>
+          <t>已覆盖</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>整体停留在“数据工具作业”，未升到“月度盘点管理闭环”</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t>补反馈收集、评估缺口、结论形成，与规划衔接</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="10" t="inlineStr">
-        <is>
-          <t>三、建议的月度节奏（便于落地）</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="80" customHeight="1">
-      <c r="A23" s="13" t="inlineStr">
-        <is>
-          <t>月初第1-2个工作日：步骤1-2取数与生成分析表；
-第3-4个工作日：步骤3异常识别 + 步骤4反馈收集（可并行）；
-第5-8个工作日：步骤5整改闭环（可滚动到月中）；
-月中前：步骤6评估与缺口识别；
-固定截止日：步骤7结论确认 + 步骤8发布并移交规划。</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="10" t="inlineStr">
-        <is>
-          <t>四、与AI适配的初步提示（本表暂不展开AI工作流，待确认后下一步细化）</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="60" customHeight="1">
-      <c r="A26" s="13" t="inlineStr">
-        <is>
-          <t>高适配候选：步骤2汇总清洗、步骤3异常初筛、步骤6缺口/标签建议草稿、步骤7结论初稿；
-必须人工确认：整改催办策略、盘点结论发布、下架/紧急开发等决策；
-低优先级/已有工具：步骤1取数（偏系统集成）、步骤8多渠道分发（偏自动化）。</t>
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>评估表+标签建议+缺口/紧急需求</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>AI步骤6</t>
+        </is>
+      </c>
+      <c r="C19" s="16" t="inlineStr">
+        <is>
+          <t>已覆盖</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>月度盘点结论+需求/迭代建议</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>AI步骤6+7</t>
+        </is>
+      </c>
+      <c r="C20" s="16" t="inlineStr">
+        <is>
+          <t>已覆盖</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>管理员课程清单+同步+移交规划</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>AI步骤7</t>
+        </is>
+      </c>
+      <c r="C21" s="16" t="inlineStr">
+        <is>
+          <t>已覆盖</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="1">
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A23:D23"/>
-    <mergeCell ref="A26:D26"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1317,7 +1513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1330,74 +1526,81 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
+        <is>
+          <t>月度盘点 · 原有工作流（已确认，8步）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>步骤</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>环节名称</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>现在由谁做</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>当前做法</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
         <is>
           <t>输入材料</t>
         </is>
       </c>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>输出结果</t>
         </is>
       </c>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>当前问题</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="90" customHeight="1">
-      <c r="A2" s="4" t="n">
+    <row r="3" ht="95" customHeight="1">
+      <c r="A3" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B3" s="7" t="inlineStr">
         <is>
           <t>多源取数与基础表导入</t>
         </is>
       </c>
-      <c r="C2" s="5" t="inlineStr">
+      <c r="C3" s="7" t="inlineStr">
         <is>
           <t>罗阳先</t>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="D3" s="7" t="inlineStr">
         <is>
           <t>1. 从海味平台后台、知识库、组织/花名册等源系统分别导出原始 Excel；
 2. 将可用课程清单、在线课程导出、在线课程学习表、个人学习情况（周/年）、知识管理、员工花名册等导入自制分析工具（SQLite）；
 3. 校验表名与列名是否匹配白名单，不合格则退回重导。</t>
         </is>
       </c>
-      <c r="E2" s="5" t="inlineStr">
+      <c r="E3" s="7" t="inlineStr">
         <is>
           <t>平台后台、知识库、花名册等原始数据；上月运营相关导出权限</t>
         </is>
       </c>
-      <c r="F2" s="5" t="inlineStr">
+      <c r="F3" s="7" t="inlineStr">
         <is>
           <t>SQLite 中 7 张基础表（可用课程清单、在线课程导出、在线课程学习表、个人学习情况周、个人学习情况年、知识管理、员工花名册）</t>
         </is>
       </c>
-      <c r="G2" s="5" t="inlineStr">
+      <c r="G3" s="7" t="inlineStr">
         <is>
           <t>①数据分散在多系统，需反复手工导出，耗时长、易漏导；
 ②列名/格式须严格匹配，非白名单表不可导入，失败后需重跑；
@@ -1405,36 +1608,36 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="90" customHeight="1">
-      <c r="A3" s="4" t="n">
+    <row r="4" ht="95" customHeight="1">
+      <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>分析表生成（清单+使用统计）</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>罗阳先</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>使用自制软件按固定顺序对基础表进行分析汇总，生成课程清单类与统计类结果表；同时汇总上月浏览/学习人数/完成率/时长等使用指标，为后续异常识别做准备。</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr">
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>上述 7 张基础表</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>海味课程月度清单、海味课程目录、课程数据统计、上周/上月新课清单、上周/上月新知识清单；上月资源使用统计底表</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="G4" s="7" t="inlineStr">
         <is>
           <t>①须先导齐全部基础表，依赖顺序强，失败需整段重跑；
 ②大表运算偏慢；
@@ -1442,38 +1645,38 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="90" customHeight="1">
-      <c r="A4" s="4" t="n">
+    <row r="5" ht="95" customHeight="1">
+      <c r="A5" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>异常与信息不规范识别</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C5" s="7" t="inlineStr">
         <is>
           <t>罗阳先</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D5" s="7" t="inlineStr">
         <is>
           <t>1. 在海味课程月度清单中核查目录、部门归属、标题、课程简介、讲师、封面、标签、大纲、面向对象等字段是否规范完整；
 2. 结合使用统计，识别异常资源（如完成率骤降、零学习、差评集中、长期无更新等）；
 3. 形成待整改清单与异常初判清单。</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E5" s="7" t="inlineStr">
         <is>
           <t>海味课程月度清单、课程数据统计/使用统计底表、盘点核对标准（如有）</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="F5" s="7" t="inlineStr">
         <is>
           <t>信息不规范课程清单；使用异常资源初判清单；拟整改项说明</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="G5" s="7" t="inlineStr">
         <is>
           <t>①异常识别高度依赖个人经验，规则未固化，易遗漏；
 ②信息不规范与使用异常两套判断混在一起，缺少标准检查清单；
@@ -1481,38 +1684,38 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="90" customHeight="1">
-      <c r="A5" s="4" t="n">
+    <row r="6" ht="95" customHeight="1">
+      <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>业务变化与用户/业务反馈收集</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>罗阳先（牵头）；业务方/分院管理员（提供反馈）</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>1. 收集本月业务发展变化、战略/项目重点调整信息；
 2. 汇总用户与业务方对资源的反馈（缺失主题、内容过时、急需补课等）；
 3. 调阅上期盘点结论与未闭环事项，形成本月输入包。</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>业务需求变更信息、用户/业务方反馈、上期盘点结论与待办、相关会议纪要或飞书文档</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>本月业务变化与反馈汇总表；上期未闭环事项清单</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="G6" s="7" t="inlineStr">
         <is>
           <t>①反馈渠道分散（群聊、口头、文档），收集不完整、难结构化；
 ②缺少固定收集节奏与责任人，容易遗漏紧急需求；
@@ -1520,36 +1723,36 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="90" customHeight="1">
-      <c r="A6" s="4" t="n">
+    <row r="7" ht="95" customHeight="1">
+      <c r="A7" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>课程信息整改闭环</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C7" s="7" t="inlineStr">
         <is>
           <t>罗阳先（发起与跟踪）；课程发布人（修改落地）</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D7" s="7" t="inlineStr">
         <is>
           <t>依据信息不规范清单，联系对应课程发布人，在海味平台完成目录、归属、标题、简介、讲师、封面、标签、大纲、面向对象等字段整改；罗阳先复核是否达标。</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E7" s="7" t="inlineStr">
         <is>
           <t>信息不规范课程清单；课程发布人联系方式；平台编辑权限</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="F7" s="7" t="inlineStr">
         <is>
           <t>已整改课程清单；未整改/超期清单；平台侧字段更新结果</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="G7" s="7" t="inlineStr">
         <is>
           <t>①靠人工逐个联系催改，协同成本高、进度不可视；
 ②发布人响应不及时导致盘点结论滞后；
@@ -1557,38 +1760,38 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="90" customHeight="1">
-      <c r="A7" s="4" t="n">
+    <row r="8" ht="95" customHeight="1">
+      <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B8" s="7" t="inlineStr">
         <is>
           <t>重点资源评估与缺口/紧急需求识别</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>罗阳先（初评）；业务专家/管理员（确认）</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D8" s="7" t="inlineStr">
         <is>
           <t>1. 结合使用数据、异常清单、业务反馈，对重点资源做月度评估；
 2. 识别新增缺口与紧急需求（主题、对象、形式、优先级）；
 3. 滚动更新资源健康度/运营标签建议（高价值/待优化/建议下架等，月度以滚动更新为主）。</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>使用统计与异常清单、业务变化与反馈汇总、上期缺口清单、资源目录</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t>重点资源评估表；新增缺口与紧急需求清单；资源标签更新建议</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="G8" s="7" t="inlineStr">
         <is>
           <t>①评估标准不统一，经验依赖强；
 ②缺口与紧急需求缺少量化优先级；
@@ -1596,36 +1799,36 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="90" customHeight="1">
-      <c r="A8" s="4" t="n">
+    <row r="9" ht="95" customHeight="1">
+      <c r="A9" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B9" s="7" t="inlineStr">
         <is>
           <t>形成月度盘点结论</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C9" s="7" t="inlineStr">
         <is>
           <t>罗阳先（起草）；业务专家（确认）</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D9" s="7" t="inlineStr">
         <is>
           <t>汇总本月清单治理结果、使用与异常洞察、反馈与缺口识别，形成《月度盘点结论》（含：现状摘要、异常与整改情况、缺口与紧急需求、迭代建议、需规划承接事项）。</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="E9" s="7" t="inlineStr">
         <is>
           <t>已整改结果、异常与评估表、缺口与紧急需求清单、上期盘点结论</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="F9" s="7" t="inlineStr">
         <is>
           <t>《月度盘点结论》；滚动更新后的资源需求/迭代建议清单</t>
         </is>
       </c>
-      <c r="G8" s="5" t="inlineStr">
+      <c r="G9" s="7" t="inlineStr">
         <is>
           <t>①从多份表到成文靠人工拼接，耗时长；
 ②结论口径月度间不一致，难对比；
@@ -1633,42 +1836,154 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="90" customHeight="1">
-      <c r="A9" s="4" t="n">
+    <row r="10" ht="95" customHeight="1">
+      <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B10" s="7" t="inlineStr">
         <is>
           <t>结果发布与管理员同步</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>罗阳先</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D10" s="7" t="inlineStr">
         <is>
           <t>1. 发布《海味课程月度清单》供各级管理员查阅使用（因其日常权限无法看全平台课程）；
 2. 同步月度盘点结论、缺口/需求清单至飞书等渠道；
 3. 将需规划承接事项移交“线上学习资源规划”。</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>海味课程月度清单终版、《月度盘点结论》、资源需求/迭代建议清单</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>管理员可用的全量/月度课程清单；已同步的盘点结论与需求清单；向规划环节的移交记录</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="G10" s="7" t="inlineStr">
         <is>
           <t>①与飞书等汇报渠道仍需人工粘贴，无自动对接；
 ②清单、结论、需求多份材料分发，版本易乱；
 ③管理员是否取用、是否反馈缺少闭环。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:G1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="80" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="13" t="inlineStr">
+        <is>
+          <t>确认记录与下一步</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="14" t="inlineStr">
+        <is>
+          <t>已确认</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>原有工作流8步已确认；并据此完成AI优化后工作流7步填写。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="14" t="inlineStr">
+        <is>
+          <t>AI优化后7步（摘要）</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="17" t="inlineStr">
+        <is>
+          <t>1. 取数批次发起与质量校验</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="17" t="inlineStr">
+        <is>
+          <t>2. 分析表与使用洞察自动生成</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="17" t="inlineStr">
+        <is>
+          <t>3. 不规范与使用异常智能初筛</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="17" t="inlineStr">
+        <is>
+          <t>4. 反馈结构化归并与缺口关联</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="17" t="inlineStr">
+        <is>
+          <t>5. 整改工单催办与合规复检</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="17" t="inlineStr">
+        <is>
+          <t>6. 评估/标签/缺口建议生成</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="17" t="inlineStr">
+        <is>
+          <t>7. 结论成文、清单发布与同步</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="14" t="inlineStr">
+        <is>
+          <t>建议下一步</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="50" customHeight="1">
+      <c r="A16" s="18" t="inlineStr">
+        <is>
+          <t>1）确认右侧AI步骤与人工确认点是否认可；
+2）如认可，可继续细化异常规则清单、输出物模板字段、以及优先落地的AI节点（建议优先：步骤2/3/6/7）。</t>
         </is>
       </c>
     </row>

--- a/docs/ai-workshop/月度盘点工作流拆解-补充版.xlsx
+++ b/docs/ai-workshop/月度盘点工作流拆解-补充版.xlsx
@@ -672,26 +672,24 @@
       </c>
       <c r="G4" s="7" t="inlineStr">
         <is>
-          <t>1. 设定本月盘点范围与取数批次，发起取数；
-2. 处理校验失败项并补导缺失表；
-3. 确认本月口径（人数/完成率等）无争议。</t>
+          <t>1. 确认本月盘点范围与口径（含人数/完成率等指标口径）
+2. 审定取数批次与白名单规则
+3. 对缺失表/异常字段补导决策做最终放行</t>
         </is>
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>1. 按白名单校验表名/列名/必填字段；
-2. 生成取数完整性与口径差异报告；
-3. 标记缺失表、异常字段与建议重导清单。</t>
+          <t>按白名单校验表名/列名/必填字段；生成取数完整性与口径差异报告；识别缺失表、异常字段并给出重导清单</t>
         </is>
       </c>
       <c r="I4" s="7" t="inlineStr">
         <is>
-          <t>规则校验 + 数据质量助手</t>
+          <t>规则校验（表结构/字段约束）+ 口径参数化模板</t>
         </is>
       </c>
       <c r="J4" s="7" t="inlineStr">
         <is>
-          <t>已校验基础数据集（含批次号）；取数质量报告；待补导清单</t>
+          <t>取数质量校验报告；缺失表/字段补导清单（含原因与建议处理方式）</t>
         </is>
       </c>
       <c r="K4" s="8" t="inlineStr">
@@ -734,26 +732,24 @@
       </c>
       <c r="G5" s="10" t="inlineStr">
         <is>
-          <t>1. 确认分析表生成成功；
-2. 抽检关键指标口径；
-3. 确定本月重点关注资源范围。</t>
+          <t>1. 审定分析表生成成功
+2. 抽检关键指标口径无误
+3. 确认本月重点资源评估范围与统计粒度</t>
         </is>
       </c>
       <c r="H5" s="10" t="inlineStr">
         <is>
-          <t>1. 自动汇总生成课程月度清单、目录、统计、新课/新知识表；
-2. 汇总上月使用指标（学习人数、完成率、时长等）；
-3. 输出使用洞察草稿（环比异动、头部/尾部资源）。</t>
+          <t>自动汇总生成课程月度清单、目录、统计表、新课/新知识表；并汇总上月使用指标（环比对比）输出使用洞察草稿</t>
         </is>
       </c>
       <c r="I5" s="10" t="inlineStr">
         <is>
-          <t>数据分析助手（汇总统计 + 洞察草稿）</t>
+          <t>数据统计汇总 + 差异洞察生成</t>
         </is>
       </c>
       <c r="J5" s="10" t="inlineStr">
         <is>
-          <t>分析表全套；上月使用统计底表；使用洞察草稿</t>
+          <t>分析表全套；上月使用统计底表；使用洞察草稿（异常变化点列表）</t>
         </is>
       </c>
       <c r="K5" s="8" t="inlineStr">
@@ -798,26 +794,24 @@
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
-          <t>1. 审定异常规则阈值；
-2. 确认不规范字段判定标准；
-3. 裁定争议项（误报剔除/漏报复核）。</t>
+          <t>1. 审定“不规范字段”判定标准/阈值
+2. 对异常初筛结果做复核（误报剔除/漏报补充）
+3. 确认最终不规范清单与使用异常清单</t>
         </is>
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>1. 按规则+语义检查识别字段不规范（目录/归属/标题/简介/讲师/封面/标签/大纲/对象等）；
-2. 识别使用异常（零学习、完成率骤降、差评集中、长期未更新等）；
-3. 输出待整改清单与异常初判清单（含理由）。</t>
+          <t>基于规则+语义检查识别目录/归属/标题/简介/讲师/封面/标签/大纲/对象等字段缺失或不一致；结合使用指标识别零学习/完成率骤降/长期未更新等异常；输出待整改清单与异常初判（含理由）</t>
         </is>
       </c>
       <c r="I6" s="7" t="inlineStr">
         <is>
-          <t>规则引擎 + LLM初筛</t>
+          <t>规则校验 + 语义初筛（文本检查/相似度判断）</t>
         </is>
       </c>
       <c r="J6" s="7" t="inlineStr">
         <is>
-          <t>信息不规范清单；使用异常初判清单；规则命中说明</t>
+          <t>不规范清单；使用异常初判清单（附命中理由/证据指向）</t>
         </is>
       </c>
       <c r="K6" s="8" t="inlineStr">
@@ -862,26 +856,24 @@
       </c>
       <c r="G7" s="10" t="inlineStr">
         <is>
-          <t>1. 发起本月反馈收集（分院/业务方）；
-2. 补充关键业务变化口头信息；
-3. 确认紧急需求优先级。</t>
+          <t>1. 发起反馈收集并确认责任方/来源
+2. 对紧急需求优先级做裁定
+3. 审定结构化归并结果（避免遗漏与错配）</t>
         </is>
       </c>
       <c r="H7" s="10" t="inlineStr">
         <is>
-          <t>1. 归并分散反馈（文档/表格/纪要）并结构化；
-2. 对照上期未闭环事项生成跟踪表；
-3. 将反馈主题与资源缺口候选自动关联。</t>
+          <t>将分散反馈归并为结构化条目（主题/对象/诉求/原因）；生成对照上期未闭环事项的跟踪表；并把反馈主题关联到缺口候选模块/资源方向（生成关联建议）</t>
         </is>
       </c>
       <c r="I7" s="10" t="inlineStr">
         <is>
-          <t>文档理解 + 结构化归并助手</t>
+          <t>文档理解/表述抽取 + 结构化归并 + 关联建议</t>
         </is>
       </c>
       <c r="J7" s="10" t="inlineStr">
         <is>
-          <t>业务变化与反馈汇总表；上期未闭环跟踪表；反馈-缺口关联初稿</t>
+          <t>业务变化与反馈结构化汇总表；未闭环跟踪表；反馈-缺口关联初稿</t>
         </is>
       </c>
       <c r="K7" s="8" t="inlineStr">
@@ -924,27 +916,24 @@
       </c>
       <c r="G8" s="7" t="inlineStr">
         <is>
-          <t>1. 确认整改清单与责任发布人；
-2. 下发催改并跟踪超期；
-3. 复核整改是否达标。
-（课程发布人：在平台完成修改）</t>
+          <t>1. 确认整改责任发布人（谁改、改什么）
+2. 下发催改并跟踪超期
+3. 审核整改达标（关键字段抽检/复核）</t>
         </is>
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>1. 按课程自动匹配发布人并生成催办草稿/整改说明；
-2. 汇总已改/未改/超期状态；
-3. 对已改项做字段合规复检。</t>
+          <t>自动匹配课程发布人并生成催办草稿/整改说明；汇总已改/未改/超期状态形成进度看板；对整改后字段做合规复检并输出复检结果</t>
         </is>
       </c>
       <c r="I8" s="7" t="inlineStr">
         <is>
-          <t>工单/催办助手 + 合规复检</t>
+          <t>工单/催办消息生成 + 字段合规复检</t>
         </is>
       </c>
       <c r="J8" s="7" t="inlineStr">
         <is>
-          <t>整改工单包；进度看板（已改/未改/超期）；复检结果</t>
+          <t>整改工单包；进度看板（已改/未改/超期）；复检结果与待复核项</t>
         </is>
       </c>
       <c r="K8" s="8" t="inlineStr">
@@ -989,26 +978,24 @@
       </c>
       <c r="G9" s="10" t="inlineStr">
         <is>
-          <t>1. 确认重点资源评估结论；
-2. 裁定标签更新与缺口/紧急需求优先级；
-3. 明确需移交规划的事项。</t>
+          <t>1. 审定重点资源评估结论
+2. 裁定标签更新与缺口/紧急需求优先级
+3. 确认需移交规划的承接事项</t>
         </is>
       </c>
       <c r="H9" s="10" t="inlineStr">
         <is>
-          <t>1. 综合使用数据、异常、反馈生成重点资源评估草稿；
-2. 给出健康度/运营标签建议与缺口、紧急需求清单草稿；
-3. 提出迭代建议与规划承接建议。</t>
+          <t>综合使用统计、异常与反馈生成重点资源评估草稿；给出健康度/运营标签建议；生成缺口与紧急需求清单草稿及迭代建议方向</t>
         </is>
       </c>
       <c r="I9" s="10" t="inlineStr">
         <is>
-          <t>评估建议助手（多源综合推理）</t>
+          <t>多源综合评估（规则量化 + 大模型推理解释）</t>
         </is>
       </c>
       <c r="J9" s="10" t="inlineStr">
         <is>
-          <t>重点资源评估表；标签更新建议；缺口与紧急需求清单；迭代建议草稿</t>
+          <t>重点资源评估表；标签更新建议；缺口与紧急需求清单草稿；迭代建议草稿</t>
         </is>
       </c>
       <c r="K9" s="8" t="inlineStr">
@@ -1051,26 +1038,24 @@
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
-          <t>1. 审定《月度盘点结论》并发布；
-2. 确认管理员清单终版；
-3. 将规划承接事项正式移交。</t>
+          <t>1. 审定《月度盘点结论》终稿并发布
+2. 确认管理员清单终版（口径一致）
+3. 完成向规划环节的正式移交与留痕</t>
         </is>
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>1. 一键生成《月度盘点结论》初稿（现状/异常与整改/缺口/迭代建议）；
-2. 生成面向管理员的清单说明与飞书同步文案；
-3. 检查本月交付物是否齐全（结论、标签建议、需求清单、课程清单）。</t>
+          <t>自动生成《月度盘点结论》初稿（现状/异常与整改/缺口/建议）；生成面向管理员的清单说明与同步文案；校验交付物齐全性与版本一致性，输出发布清单</t>
         </is>
       </c>
       <c r="I10" s="7" t="inlineStr">
         <is>
-          <t>报告生成助手 + 分发文案助手</t>
+          <t>报告生成 + 文案生成 + 交付物一致性校验</t>
         </is>
       </c>
       <c r="J10" s="7" t="inlineStr">
         <is>
-          <t>《月度盘点结论》初稿/定稿稿；管理员课程清单终版；同步文案；交付物齐全性检查结果；规划移交清单</t>
+          <t>月度盘点结论初稿/定稿稿；管理员课程清单终版说明；同步文案；交付物发布校验结果；移交清单</t>
         </is>
       </c>
       <c r="K10" s="8" t="inlineStr">
